--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>2276.0</v>
+        <v>2278.0</v>
       </c>
       <c r="G3" t="n">
         <v>12.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1674.0</v>
+        <v>1683.0</v>
       </c>
       <c r="G2" t="n">
         <v>4.0</v>
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>2278.0</v>
+        <v>2280.0</v>
       </c>
       <c r="G3" t="n">
         <v>12.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1683.0</v>
+        <v>1687.0</v>
       </c>
       <c r="G2" t="n">
         <v>4.0</v>
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>2280.0</v>
+        <v>2281.0</v>
       </c>
       <c r="G3" t="n">
         <v>12.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1687.0</v>
+        <v>1690.0</v>
       </c>
       <c r="G2" t="n">
         <v>4.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1690.0</v>
+        <v>1694.0</v>
       </c>
       <c r="G2" t="n">
         <v>4.0</v>
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>2281.0</v>
+        <v>2283.0</v>
       </c>
       <c r="G3" t="n">
         <v>12.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1694.0</v>
+        <v>1695.0</v>
       </c>
       <c r="G2" t="n">
         <v>4.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1695.0</v>
+        <v>1704.0</v>
       </c>
       <c r="G2" t="n">
         <v>4.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1704.0</v>
+        <v>1709.0</v>
       </c>
       <c r="G2" t="n">
         <v>4.0</v>
@@ -176,10 +176,10 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>2283.0</v>
+        <v>3867.0</v>
       </c>
       <c r="G3" t="n">
-        <v>12.0</v>
+        <v>22.0</v>
       </c>
       <c r="H3" t="n">
         <v>93.0</v>
@@ -254,7 +254,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>55.0</v>
+        <v>188.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1709.0</v>
+        <v>1710.0</v>
       </c>
       <c r="G2" t="n">
         <v>4.0</v>
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3867.0</v>
+        <v>3868.0</v>
       </c>
       <c r="G3" t="n">
         <v>22.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1710.0</v>
+        <v>1715.0</v>
       </c>
       <c r="G2" t="n">
         <v>4.0</v>
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3868.0</v>
+        <v>3872.0</v>
       </c>
       <c r="G3" t="n">
         <v>22.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,10 +150,10 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1715.0</v>
+        <v>1720.0</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="H2" t="n">
         <v>6.0</v>
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3872.0</v>
+        <v>3873.0</v>
       </c>
       <c r="G3" t="n">
         <v>22.0</v>
@@ -254,7 +254,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,10 +153,10 @@
         <v>1720.0</v>
       </c>
       <c r="G2" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="H2" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="3">
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3873.0</v>
+        <v>3878.0</v>
       </c>
       <c r="G3" t="n">
         <v>22.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,13 +150,13 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1720.0</v>
+        <v>1730.0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="H2" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="3">
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3878.0</v>
+        <v>3880.0</v>
       </c>
       <c r="G3" t="n">
         <v>22.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3880.0</v>
+        <v>3882.0</v>
       </c>
       <c r="G3" t="n">
         <v>22.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1730.0</v>
+        <v>1733.0</v>
       </c>
       <c r="G2" t="n">
         <v>12.0</v>
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3882.0</v>
+        <v>3884.0</v>
       </c>
       <c r="G3" t="n">
         <v>22.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1733.0</v>
+        <v>1734.0</v>
       </c>
       <c r="G2" t="n">
         <v>12.0</v>
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3884.0</v>
+        <v>3885.0</v>
       </c>
       <c r="G3" t="n">
         <v>22.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1734.0</v>
+        <v>1736.0</v>
       </c>
       <c r="G2" t="n">
         <v>12.0</v>
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3885.0</v>
+        <v>3887.0</v>
       </c>
       <c r="G3" t="n">
         <v>22.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,10 +150,10 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1736.0</v>
+        <v>1752.0</v>
       </c>
       <c r="G2" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>
@@ -176,10 +176,10 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3887.0</v>
+        <v>3894.0</v>
       </c>
       <c r="G3" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="H3" t="n">
         <v>93.0</v>
@@ -254,7 +254,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,7 +153,7 @@
         <v>1752.0</v>
       </c>
       <c r="G2" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1752.0</v>
+        <v>1755.0</v>
       </c>
       <c r="G2" t="n">
         <v>15.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,10 +150,10 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1755.0</v>
+        <v>1763.0</v>
       </c>
       <c r="G2" t="n">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3894.0</v>
+        <v>3896.0</v>
       </c>
       <c r="G3" t="n">
         <v>23.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,10 +150,10 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1763.0</v>
+        <v>1767.0</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>
@@ -176,10 +176,10 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3896.0</v>
+        <v>3898.0</v>
       </c>
       <c r="G3" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="H3" t="n">
         <v>93.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1767.0</v>
+        <v>1772.0</v>
       </c>
       <c r="G2" t="n">
         <v>4.0</v>
@@ -176,10 +176,10 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3898.0</v>
+        <v>3903.0</v>
       </c>
       <c r="G3" t="n">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="H3" t="n">
         <v>93.0</v>
@@ -254,7 +254,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -228,7 +228,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G5" t="n">
         <v>0.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1772.0</v>
+        <v>1773.0</v>
       </c>
       <c r="G2" t="n">
         <v>4.0</v>
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3903.0</v>
+        <v>3904.0</v>
       </c>
       <c r="G3" t="n">
         <v>21.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,7 +150,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1773.0</v>
+        <v>1774.0</v>
       </c>
       <c r="G2" t="n">
         <v>4.0</v>
@@ -176,7 +176,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>3904.0</v>
+        <v>3907.0</v>
       </c>
       <c r="G3" t="n">
         <v>21.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -150,10 +150,10 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1774.0</v>
+        <v>1775.0</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="17">
   <si>
     <t>Area</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Roma</t>
+  </si>
+  <si>
+    <t>Frosinone</t>
   </si>
   <si>
     <t>Viterbo</t>
@@ -147,10 +150,10 @@
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1775.0</v>
+        <v>1779.0</v>
       </c>
       <c r="G2" t="n">
         <v>6.0</v>
@@ -170,19 +173,19 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>3907.0</v>
+        <v>1.0</v>
       </c>
       <c r="G3" t="n">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="H3" t="n">
-        <v>93.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -196,19 +199,19 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0</v>
+        <v>3908.0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0</v>
+        <v>21.0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0</v>
+        <v>93.0</v>
       </c>
     </row>
     <row r="5">
@@ -216,19 +219,19 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>28.0</v>
+        <v>1.0</v>
       </c>
       <c r="G5" t="n">
         <v>0.0</v>
@@ -242,7 +245,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
@@ -251,15 +254,41 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="n">
         <v>191.0</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="G7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H7" t="n">
         <v>2.0</v>
       </c>
     </row>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,7 +153,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1779.0</v>
+        <v>1780.0</v>
       </c>
       <c r="G2" t="n">
         <v>6.0</v>
@@ -205,7 +205,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>3908.0</v>
+        <v>3909.0</v>
       </c>
       <c r="G4" t="n">
         <v>21.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,10 +153,10 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1780.0</v>
+        <v>1785.0</v>
       </c>
       <c r="G2" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>
@@ -205,7 +205,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>3909.0</v>
+        <v>3910.0</v>
       </c>
       <c r="G4" t="n">
         <v>21.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,7 +153,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1785.0</v>
+        <v>1789.0</v>
       </c>
       <c r="G2" t="n">
         <v>9.0</v>
@@ -205,7 +205,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>3910.0</v>
+        <v>3912.0</v>
       </c>
       <c r="G4" t="n">
         <v>21.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,10 +153,10 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1789.0</v>
+        <v>1791.0</v>
       </c>
       <c r="G2" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -156,7 +156,7 @@
         <v>1791.0</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,10 +153,10 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1791.0</v>
+        <v>1797.0</v>
       </c>
       <c r="G2" t="n">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>
@@ -205,7 +205,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>3912.0</v>
+        <v>3914.0</v>
       </c>
       <c r="G4" t="n">
         <v>21.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,10 +153,10 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1797.0</v>
+        <v>1814.0</v>
       </c>
       <c r="G2" t="n">
-        <v>22.0</v>
+        <v>8.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,10 +153,10 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1814.0</v>
+        <v>1815.0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>
@@ -205,7 +205,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>3914.0</v>
+        <v>3915.0</v>
       </c>
       <c r="G4" t="n">
         <v>21.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,7 +153,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1815.0</v>
+        <v>1817.0</v>
       </c>
       <c r="G2" t="n">
         <v>12.0</v>
@@ -205,7 +205,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>3915.0</v>
+        <v>3919.0</v>
       </c>
       <c r="G4" t="n">
         <v>21.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,10 +153,10 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1817.0</v>
+        <v>1819.0</v>
       </c>
       <c r="G2" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>
@@ -205,7 +205,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>3919.0</v>
+        <v>3921.0</v>
       </c>
       <c r="G4" t="n">
         <v>21.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,10 +153,10 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1819.0</v>
+        <v>1823.0</v>
       </c>
       <c r="G2" t="n">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>
@@ -205,7 +205,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>3921.0</v>
+        <v>3925.0</v>
       </c>
       <c r="G4" t="n">
         <v>21.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,7 +153,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1823.0</v>
+        <v>1824.0</v>
       </c>
       <c r="G2" t="n">
         <v>21.0</v>
@@ -205,7 +205,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>3925.0</v>
+        <v>3926.0</v>
       </c>
       <c r="G4" t="n">
         <v>21.0</v>

--- a/Download/CasiControlli_ZP.xlsx
+++ b/Download/CasiControlli_ZP.xlsx
@@ -153,10 +153,10 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1824.0</v>
+        <v>1827.0</v>
       </c>
       <c r="G2" t="n">
-        <v>21.0</v>
+        <v>30.0</v>
       </c>
       <c r="H2" t="n">
         <v>11.0</v>
@@ -179,7 +179,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -205,10 +205,10 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>3926.0</v>
+        <v>3928.0</v>
       </c>
       <c r="G4" t="n">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
       <c r="H4" t="n">
         <v>93.0</v>
